--- a/downloads/Reviewer-Response-Matrix.xlsx
+++ b/downloads/Reviewer-Response-Matrix.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R15396c7b932d4313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="Rf878a4d1dbbd43a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="Rdde86b3247be4fa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R203d8d4db2704bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="Rac049c68229c4b09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="R63cee010c3c240f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -376,7 +376,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Dental Research AI • Free, editable Excel worksheet • Version 2 • 8 September 2026</x:v>
+        <x:v>Dental Research AI • Free editable worksheet • Version 3 • 9 September 2026</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -413,7 +413,7 @@
         <x:v>1. Read the example</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>Open Completed example. Every study, event, source excerpt, tool record, and action in that sheet is invented for teaching.</x:v>
+        <x:v>Read the Completed example. Published facts are cited to JOP. Proposed plans, practice errors, imagined comments, and AI-use records are labeled teaching exercises; they are not the authors’ original records.</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Green = example</x:v>
@@ -474,12 +474,12 @@
         <x:v>Use approved storage</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="86" customHeight="1">
+    <x:row r="12" ht="150" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>Sources / limits</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>Confidentiality guidance: https://www.icmje.org/recommendations/browse/artificial-intelligence/ai-use-by-reviewers.html ; follow your own journal and institutional rules.</x:v>
+        <x:v>Omar MS, Yang CC, Morton D, Lin WS. Journal of Prosthodontics. 2026. Early View; supplied PDF pp. 1–8. Virtual articulation using sequential mandibular intraoral scans and computational functional rotation reference determination—Proof-of-concept https://onlinelibrary.wiley.com/doi/10.1111/jopr.70188 Technique, PDF pp. 2–6; Figure 8 and Discussion, PDF p. 7.</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
         <x:v>Recheck current guidance</x:v>
@@ -501,7 +501,7 @@
         <x:v>Calculation legend</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>Yellow cells are editable inputs; green cells on the example sheet contain invented entries. Dark teal total rows, if present, contain formulas. Do not replace formulas with typed totals.</x:v>
+        <x:v>Yellow cells are editable; green example cells contain published facts and clearly labeled teaching entries. Dark teal timing totals contain formulas. Preserve formulas when editing.</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
         <x:v>No color-only status codes</x:v>
@@ -684,7 +684,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76cd913f591f474b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1649696c473e4651"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -704,7 +704,7 @@
   <x:sheetData>
     <x:row r="1" ht="46" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Example: tracing replies to real changes</x:v>
+        <x:v>Example: imagined articulation review comments</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -715,7 +715,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>COMPLETED EXAMPLE • Invented study records and actions; not a real manuscript or peer review.</x:v>
+        <x:v>INVENTED REVIEW COMMENTS AND PLANNED REPLIES. Not the published article’s peer-review correspondence.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -726,7 +726,7 @@
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>Invented reviewer comments only. One completed teaching edit and two pending actions illustrate honest status tracking.</x:v>
+        <x:v>Omar et al. describe a single-case proof of concept, reported internal RMSD 0.14 mm, and compatibility with three articulator coordinate systems. Discussion, PDF p. 7. All proposed edits below are pending.</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -760,71 +760,71 @@
     </x:row>
     <x:row r="5" ht="160" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>R1.1</x:v>
+        <x:v>R1</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>Clarify experimental unit and three scans per cast.</x:v>
+        <x:v>Distinguish internal residual error from external clinical accuracy.</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
-        <x:v>Clarify that technical repeats are averaged and cast is the paired unit.</x:v>
+        <x:v>The teaching revision will explain what internal validation measures.</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str">
-        <x:v>Add and verify the Methods explanation.</x:v>
+        <x:v>Add and check a scope sentence.</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
-        <x:v>“Three technical scans were averaged within each cast/device. The cast was the paired unit.” Methods p5, lines 100–102.</x:v>
+        <x:v>NOT YET DONE. Planned teaching Discussion paragraph 2.</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Complete</x:v>
+        <x:v>Pending</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>Statistician checked teaching revision, 2026-09-08.</x:v>
+        <x:v>Methods reviewer — NOT YET DONE</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="160" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>R1.2</x:v>
+        <x:v>R2</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>The conclusion implies clinical superiority.</x:v>
+        <x:v>Do three articulators mean three patient cohorts?</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Limit conclusion to the measured laboratory outcome.</x:v>
+        <x:v>Clarify three coordinate-system implementations in one case.</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str">
-        <x:v>Revise Discussion and check Abstract.</x:v>
+        <x:v>Revise the teaching compatibility paragraph.</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
-        <x:v>NOT YET DONE. Intended location: final Discussion paragraph.</x:v>
+        <x:v>NOT YET DONE. Planned teaching Discussion paragraph 3.</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Lead author — NOT YET DONE</x:v>
+        <x:v>Course presenter — NOT YET DONE</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="160" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>R2.1</x:v>
+        <x:v>R3</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>Report scanner calibration.</x:v>
+        <x:v>Add multicenter validation.</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>Review contemporaneous logs before describing calibration.</x:v>
+        <x:v>No new participants or experiments are planned; identify independent validation as future work.</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>Laboratory lead must retrieve and check the equipment log.</x:v>
+        <x:v>Explain the study boundary without claiming new data.</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>NOT YET DONE. No calibration statement is yet verified.</x:v>
+        <x:v>NOT YET DONE. Planned teaching limitations paragraph.</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>Laboratory lead — NOT YET DONE</x:v>
+        <x:v>Principal investigator role — NOT YET DONE</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
@@ -849,7 +849,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4e9418c1e794813"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14cb2970f8ff4753"/>
   </x:tableParts>
 </x:worksheet>
 </file>